--- a/data/historial_equipos.xlsx
+++ b/data/historial_equipos.xlsx
@@ -16,7 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,6 +527,134 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CRSJ001</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ssss</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ANDRES MONTIEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CRSJ001</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>REPARACIÓN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ssssssss</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CARLOS VERGARA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRSJ200</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ANDRES MONTIEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRSJ200</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ANDRES MONTIEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CRSJ200</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>REPARACIÓN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ANDRES MONTIEL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
